--- a/jogos_2025-03-26.xlsx
+++ b/jogos_2025-03-26.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="113">
   <si>
     <t>Date</t>
   </si>
@@ -127,60 +127,6 @@
     <t>awayGoals</t>
   </si>
   <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
-  </si>
-  <si>
     <t>DateTime</t>
   </si>
   <si>
@@ -271,12 +217,12 @@
     <t>Opatija</t>
   </si>
   <si>
+    <t>Sunshine Stars</t>
+  </si>
+  <si>
     <t>Kano Pillars</t>
   </si>
   <si>
-    <t>Sunshine Stars</t>
-  </si>
-  <si>
     <t>Racing</t>
   </si>
   <si>
@@ -316,10 +262,10 @@
     <t>Rudeš</t>
   </si>
   <si>
+    <t>Heartland</t>
+  </si>
+  <si>
     <t>Bendel Insurance</t>
-  </si>
-  <si>
-    <t>Heartland</t>
   </si>
   <si>
     <t>River Plate</t>
@@ -770,10 +716,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD16"/>
+  <dimension ref="A1:AL16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -888,79 +834,25 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45742</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="E2" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="F2" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -975,7 +867,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="L2">
         <v>5.9</v>
@@ -1050,87 +942,33 @@
         <v>1.17</v>
       </c>
       <c r="AJ2" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="AK2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AL2">
-        <v>2.68</v>
-      </c>
-      <c r="AM2">
-        <v>1.13</v>
-      </c>
-      <c r="AN2">
-        <v>1.05</v>
-      </c>
-      <c r="AO2">
-        <v>8</v>
-      </c>
-      <c r="AP2">
-        <v>1.24</v>
-      </c>
-      <c r="AQ2">
-        <v>1.45</v>
-      </c>
-      <c r="AR2">
-        <v>1.81</v>
-      </c>
-      <c r="AS2">
-        <v>2.3</v>
-      </c>
-      <c r="AT2">
-        <v>3.08</v>
-      </c>
-      <c r="AU2">
-        <v>3.34</v>
-      </c>
-      <c r="AV2">
-        <v>2.41</v>
-      </c>
-      <c r="AW2">
-        <v>1.85</v>
-      </c>
-      <c r="AX2">
-        <v>1.49</v>
-      </c>
-      <c r="AY2">
-        <v>1.28</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>3.3</v>
-      </c>
-      <c r="BC2">
-        <v>1.4</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>105</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45742.33333333334</v>
       </c>
     </row>
-    <row r="3" spans="1:56">
+    <row r="3" spans="1:38">
       <c r="A3" s="2">
         <v>45742</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3" t="s">
         <v>80</v>
-      </c>
-      <c r="E3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F3" t="s">
-        <v>98</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1145,7 +983,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="L3">
         <v>2.28</v>
@@ -1220,87 +1058,33 @@
         <v>1.01</v>
       </c>
       <c r="AJ3" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AK3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AL3">
-        <v>1.25</v>
-      </c>
-      <c r="AM3">
-        <v>1.33</v>
-      </c>
-      <c r="AN3">
-        <v>1.55</v>
-      </c>
-      <c r="AO3">
-        <v>6</v>
-      </c>
-      <c r="AP3">
-        <v>0</v>
-      </c>
-      <c r="AQ3">
-        <v>0</v>
-      </c>
-      <c r="AR3">
-        <v>0</v>
-      </c>
-      <c r="AS3">
-        <v>0</v>
-      </c>
-      <c r="AT3">
-        <v>0</v>
-      </c>
-      <c r="AU3">
-        <v>0</v>
-      </c>
-      <c r="AV3">
-        <v>0</v>
-      </c>
-      <c r="AW3">
-        <v>0</v>
-      </c>
-      <c r="AX3">
-        <v>0</v>
-      </c>
-      <c r="AY3">
-        <v>0</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>1.8</v>
-      </c>
-      <c r="BC3">
-        <v>2.63</v>
-      </c>
-      <c r="BD3" s="3">
+        <v>98</v>
+      </c>
+      <c r="AL3" s="3">
         <v>45742.45833333334</v>
       </c>
     </row>
-    <row r="4" spans="1:56">
+    <row r="4" spans="1:38">
       <c r="A4" s="2">
         <v>45742</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="F4" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -1315,7 +1099,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="L4">
         <v>1.77</v>
@@ -1390,87 +1174,33 @@
         <v>1.02</v>
       </c>
       <c r="AJ4" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AK4" t="s">
-        <v>121</v>
-      </c>
-      <c r="AL4">
-        <v>1.21</v>
-      </c>
-      <c r="AM4">
-        <v>1.28</v>
-      </c>
-      <c r="AN4">
-        <v>1.66</v>
-      </c>
-      <c r="AO4">
-        <v>2</v>
-      </c>
-      <c r="AP4">
-        <v>0</v>
-      </c>
-      <c r="AQ4">
-        <v>0</v>
-      </c>
-      <c r="AR4">
-        <v>0</v>
-      </c>
-      <c r="AS4">
-        <v>0</v>
-      </c>
-      <c r="AT4">
-        <v>0</v>
-      </c>
-      <c r="AU4">
-        <v>0</v>
-      </c>
-      <c r="AV4">
-        <v>0</v>
-      </c>
-      <c r="AW4">
-        <v>0</v>
-      </c>
-      <c r="AX4">
-        <v>0</v>
-      </c>
-      <c r="AY4">
-        <v>0</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>1.73</v>
-      </c>
-      <c r="BC4">
-        <v>2.75</v>
-      </c>
-      <c r="BD4" s="3">
+        <v>103</v>
+      </c>
+      <c r="AL4" s="3">
         <v>45742.47916666666</v>
       </c>
     </row>
-    <row r="5" spans="1:56">
+    <row r="5" spans="1:38">
       <c r="A5" s="2">
         <v>45742</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="E5" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="F5" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1485,37 +1215,37 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="L5">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="M5">
-        <v>3.18</v>
+        <v>3.34</v>
       </c>
       <c r="N5">
-        <v>5.99</v>
+        <v>4.99</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R5">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="S5">
-        <v>2.15</v>
+        <v>2.46</v>
       </c>
       <c r="T5">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="U5">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="V5">
         <v>0</v>
@@ -1524,123 +1254,69 @@
         <v>0</v>
       </c>
       <c r="X5">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="Y5">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
       <c r="Z5">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="AA5">
-        <v>2.15</v>
+        <v>2.74</v>
       </c>
       <c r="AB5">
-        <v>2.65</v>
+        <v>2.14</v>
       </c>
       <c r="AC5">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="AD5">
-        <v>5.3</v>
+        <v>3.76</v>
       </c>
       <c r="AE5">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AF5">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="AG5">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ5" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s">
-        <v>116</v>
-      </c>
-      <c r="AL5">
-        <v>1.08</v>
-      </c>
-      <c r="AM5">
-        <v>1.28</v>
-      </c>
-      <c r="AN5">
-        <v>2.15</v>
-      </c>
-      <c r="AO5">
-        <v>-1</v>
-      </c>
-      <c r="AP5">
-        <v>0</v>
-      </c>
-      <c r="AQ5">
-        <v>0</v>
-      </c>
-      <c r="AR5">
-        <v>0</v>
-      </c>
-      <c r="AS5">
-        <v>0</v>
-      </c>
-      <c r="AT5">
-        <v>0</v>
-      </c>
-      <c r="AU5">
-        <v>0</v>
-      </c>
-      <c r="AV5">
-        <v>0</v>
-      </c>
-      <c r="AW5">
-        <v>0</v>
-      </c>
-      <c r="AX5">
-        <v>0</v>
-      </c>
-      <c r="AY5">
-        <v>0</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>0</v>
-      </c>
-      <c r="BC5">
-        <v>0</v>
-      </c>
-      <c r="BD5" s="3">
+        <v>98</v>
+      </c>
+      <c r="AL5" s="3">
         <v>45742.5</v>
       </c>
     </row>
-    <row r="6" spans="1:56">
+    <row r="6" spans="1:38">
       <c r="A6" s="2">
         <v>45742</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="F6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1655,37 +1331,37 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="L6">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="M6">
-        <v>3.34</v>
+        <v>3.18</v>
       </c>
       <c r="N6">
-        <v>4.99</v>
+        <v>5.99</v>
       </c>
       <c r="O6">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="S6">
-        <v>2.46</v>
+        <v>2.15</v>
       </c>
       <c r="T6">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="U6">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="V6">
         <v>0</v>
@@ -1694,123 +1370,69 @@
         <v>0</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="Y6">
-        <v>7.1</v>
+        <v>5.5</v>
       </c>
       <c r="Z6">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="AA6">
-        <v>2.74</v>
+        <v>2.15</v>
       </c>
       <c r="AB6">
-        <v>2.14</v>
+        <v>2.65</v>
       </c>
       <c r="AC6">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="AD6">
-        <v>3.76</v>
+        <v>5.3</v>
       </c>
       <c r="AE6">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AF6">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="AG6">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AH6">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="AK6" t="s">
-        <v>116</v>
-      </c>
-      <c r="AL6">
-        <v>1.1</v>
-      </c>
-      <c r="AM6">
-        <v>1.24</v>
-      </c>
-      <c r="AN6">
-        <v>1.99</v>
-      </c>
-      <c r="AO6">
-        <v>-1</v>
-      </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6">
-        <v>0</v>
-      </c>
-      <c r="AV6">
-        <v>0</v>
-      </c>
-      <c r="AW6">
-        <v>0</v>
-      </c>
-      <c r="AX6">
-        <v>0</v>
-      </c>
-      <c r="AY6">
-        <v>0</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>1.44</v>
-      </c>
-      <c r="BC6">
-        <v>3.4</v>
-      </c>
-      <c r="BD6" s="3">
+        <v>98</v>
+      </c>
+      <c r="AL6" s="3">
         <v>45742.5</v>
       </c>
     </row>
-    <row r="7" spans="1:56">
+    <row r="7" spans="1:38">
       <c r="A7" s="2">
         <v>45742</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="E7" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="F7" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1825,7 +1447,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="L7">
         <v>2.04</v>
@@ -1900,87 +1522,33 @@
         <v>1.06</v>
       </c>
       <c r="AJ7" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="AK7" t="s">
-        <v>116</v>
-      </c>
-      <c r="AL7">
-        <v>1.24</v>
-      </c>
-      <c r="AM7">
-        <v>1.29</v>
-      </c>
-      <c r="AN7">
-        <v>1.83</v>
-      </c>
-      <c r="AO7">
-        <v>3</v>
-      </c>
-      <c r="AP7">
-        <v>1.34</v>
-      </c>
-      <c r="AQ7">
-        <v>1.58</v>
-      </c>
-      <c r="AR7">
-        <v>1.95</v>
-      </c>
-      <c r="AS7">
-        <v>2.45</v>
-      </c>
-      <c r="AT7">
-        <v>3.15</v>
-      </c>
-      <c r="AU7">
-        <v>2.9</v>
-      </c>
-      <c r="AV7">
-        <v>2.2</v>
-      </c>
-      <c r="AW7">
-        <v>1.75</v>
-      </c>
-      <c r="AX7">
-        <v>1.48</v>
-      </c>
-      <c r="AY7">
-        <v>1.29</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>1.57</v>
-      </c>
-      <c r="BC7">
-        <v>2.4</v>
-      </c>
-      <c r="BD7" s="3">
+        <v>98</v>
+      </c>
+      <c r="AL7" s="3">
         <v>45742.58333333334</v>
       </c>
     </row>
-    <row r="8" spans="1:56">
+    <row r="8" spans="1:38">
       <c r="A8" s="2">
         <v>45742</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="F8" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1995,7 +1563,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="L8">
         <v>3.3</v>
@@ -2070,87 +1638,33 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="AK8" t="s">
-        <v>124</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>0</v>
-      </c>
-      <c r="AO8">
-        <v>7</v>
-      </c>
-      <c r="AP8">
-        <v>0</v>
-      </c>
-      <c r="AQ8">
-        <v>0</v>
-      </c>
-      <c r="AR8">
-        <v>0</v>
-      </c>
-      <c r="AS8">
-        <v>0</v>
-      </c>
-      <c r="AT8">
-        <v>0</v>
-      </c>
-      <c r="AU8">
-        <v>0</v>
-      </c>
-      <c r="AV8">
-        <v>0</v>
-      </c>
-      <c r="AW8">
-        <v>0</v>
-      </c>
-      <c r="AX8">
-        <v>0</v>
-      </c>
-      <c r="AY8">
-        <v>0</v>
-      </c>
-      <c r="AZ8">
-        <v>0</v>
-      </c>
-      <c r="BA8">
-        <v>0</v>
-      </c>
-      <c r="BB8">
-        <v>2.6</v>
-      </c>
-      <c r="BC8">
-        <v>1.53</v>
-      </c>
-      <c r="BD8" s="3">
+        <v>106</v>
+      </c>
+      <c r="AL8" s="3">
         <v>45742.625</v>
       </c>
     </row>
-    <row r="9" spans="1:56">
+    <row r="9" spans="1:38">
       <c r="A9" s="2">
         <v>45742</v>
       </c>
       <c r="B9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" t="s">
         <v>62</v>
       </c>
-      <c r="C9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" t="s">
-        <v>80</v>
-      </c>
       <c r="E9" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="F9" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2165,7 +1679,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="L9">
         <v>2.31</v>
@@ -2240,87 +1754,33 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="AK9" t="s">
-        <v>125</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>0</v>
-      </c>
-      <c r="AN9">
-        <v>0</v>
-      </c>
-      <c r="AO9">
-        <v>9</v>
-      </c>
-      <c r="AP9">
-        <v>0</v>
-      </c>
-      <c r="AQ9">
-        <v>0</v>
-      </c>
-      <c r="AR9">
-        <v>0</v>
-      </c>
-      <c r="AS9">
-        <v>0</v>
-      </c>
-      <c r="AT9">
-        <v>0</v>
-      </c>
-      <c r="AU9">
-        <v>0</v>
-      </c>
-      <c r="AV9">
-        <v>0</v>
-      </c>
-      <c r="AW9">
-        <v>0</v>
-      </c>
-      <c r="AX9">
-        <v>0</v>
-      </c>
-      <c r="AY9">
-        <v>0</v>
-      </c>
-      <c r="AZ9">
-        <v>0</v>
-      </c>
-      <c r="BA9">
-        <v>0</v>
-      </c>
-      <c r="BB9">
-        <v>1.91</v>
-      </c>
-      <c r="BC9">
-        <v>2.38</v>
-      </c>
-      <c r="BD9" s="3">
+        <v>107</v>
+      </c>
+      <c r="AL9" s="3">
         <v>45742.66666666666</v>
       </c>
     </row>
-    <row r="10" spans="1:56">
+    <row r="10" spans="1:38">
       <c r="A10" s="2">
         <v>45742</v>
       </c>
       <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" t="s">
         <v>63</v>
       </c>
-      <c r="C10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D10" t="s">
-        <v>81</v>
-      </c>
       <c r="E10" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F10" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -2335,7 +1795,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="L10">
         <v>3.77</v>
@@ -2410,87 +1870,33 @@
         <v>1.15</v>
       </c>
       <c r="AJ10" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK10" t="s">
-        <v>126</v>
-      </c>
-      <c r="AL10">
-        <v>1.8</v>
-      </c>
-      <c r="AM10">
-        <v>1.27</v>
-      </c>
-      <c r="AN10">
-        <v>1.28</v>
-      </c>
-      <c r="AO10">
-        <v>10</v>
-      </c>
-      <c r="AP10">
-        <v>1.31</v>
-      </c>
-      <c r="AQ10">
-        <v>1.7</v>
-      </c>
-      <c r="AR10">
-        <v>2.01</v>
-      </c>
-      <c r="AS10">
-        <v>2.62</v>
-      </c>
-      <c r="AT10">
-        <v>3.68</v>
-      </c>
-      <c r="AU10">
-        <v>2.92</v>
-      </c>
-      <c r="AV10">
-        <v>2.05</v>
-      </c>
-      <c r="AW10">
-        <v>1.68</v>
-      </c>
-      <c r="AX10">
-        <v>1.38</v>
-      </c>
-      <c r="AY10">
-        <v>1.2</v>
-      </c>
-      <c r="AZ10">
-        <v>0</v>
-      </c>
-      <c r="BA10">
-        <v>0</v>
-      </c>
-      <c r="BB10">
-        <v>2.5</v>
-      </c>
-      <c r="BC10">
-        <v>1.57</v>
-      </c>
-      <c r="BD10" s="3">
+        <v>108</v>
+      </c>
+      <c r="AL10" s="3">
         <v>45742.6875</v>
       </c>
     </row>
-    <row r="11" spans="1:56">
+    <row r="11" spans="1:38">
       <c r="A11" s="2">
         <v>45742</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="E11" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="F11" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2505,7 +1911,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="L11">
         <v>2.17</v>
@@ -2580,87 +1986,33 @@
         <v>1.08</v>
       </c>
       <c r="AJ11" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="AK11" t="s">
-        <v>127</v>
-      </c>
-      <c r="AL11">
-        <v>1.31</v>
-      </c>
-      <c r="AM11">
-        <v>1.28</v>
-      </c>
-      <c r="AN11">
-        <v>1.6</v>
-      </c>
-      <c r="AO11">
-        <v>11</v>
-      </c>
-      <c r="AP11">
-        <v>0</v>
-      </c>
-      <c r="AQ11">
-        <v>0</v>
-      </c>
-      <c r="AR11">
-        <v>2</v>
-      </c>
-      <c r="AS11">
-        <v>0</v>
-      </c>
-      <c r="AT11">
-        <v>0</v>
-      </c>
-      <c r="AU11">
-        <v>0</v>
-      </c>
-      <c r="AV11">
-        <v>0</v>
-      </c>
-      <c r="AW11">
-        <v>1.8</v>
-      </c>
-      <c r="AX11">
-        <v>0</v>
-      </c>
-      <c r="AY11">
-        <v>0</v>
-      </c>
-      <c r="AZ11">
-        <v>0</v>
-      </c>
-      <c r="BA11">
-        <v>0</v>
-      </c>
-      <c r="BB11">
-        <v>1.73</v>
-      </c>
-      <c r="BC11">
-        <v>2.4</v>
-      </c>
-      <c r="BD11" s="3">
+        <v>109</v>
+      </c>
+      <c r="AL11" s="3">
         <v>45742.70833333334</v>
       </c>
     </row>
-    <row r="12" spans="1:56">
+    <row r="12" spans="1:38">
       <c r="A12" s="2">
         <v>45742</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" t="s">
         <v>74</v>
       </c>
-      <c r="D12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" t="s">
-        <v>92</v>
-      </c>
       <c r="F12" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2675,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="L12">
         <v>3.21</v>
@@ -2750,87 +2102,33 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="AK12" t="s">
-        <v>128</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>0</v>
-      </c>
-      <c r="AO12">
-        <v>9</v>
-      </c>
-      <c r="AP12">
-        <v>0</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
-      <c r="AR12">
-        <v>0</v>
-      </c>
-      <c r="AS12">
-        <v>0</v>
-      </c>
-      <c r="AT12">
-        <v>0</v>
-      </c>
-      <c r="AU12">
-        <v>0</v>
-      </c>
-      <c r="AV12">
-        <v>0</v>
-      </c>
-      <c r="AW12">
-        <v>0</v>
-      </c>
-      <c r="AX12">
-        <v>0</v>
-      </c>
-      <c r="AY12">
-        <v>0</v>
-      </c>
-      <c r="AZ12">
-        <v>0</v>
-      </c>
-      <c r="BA12">
-        <v>0</v>
-      </c>
-      <c r="BB12">
-        <v>2.5</v>
-      </c>
-      <c r="BC12">
-        <v>1.67</v>
-      </c>
-      <c r="BD12" s="3">
+        <v>110</v>
+      </c>
+      <c r="AL12" s="3">
         <v>45742.79166666666</v>
       </c>
     </row>
-    <row r="13" spans="1:56">
+    <row r="13" spans="1:38">
       <c r="A13" s="2">
         <v>45742</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="F13" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2845,7 +2143,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="L13">
         <v>1.95</v>
@@ -2920,87 +2218,33 @@
         <v>1.29</v>
       </c>
       <c r="AJ13" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="AK13" t="s">
-        <v>129</v>
-      </c>
-      <c r="AL13">
-        <v>1.38</v>
-      </c>
-      <c r="AM13">
-        <v>1.25</v>
-      </c>
-      <c r="AN13">
-        <v>1.75</v>
-      </c>
-      <c r="AO13">
-        <v>11</v>
-      </c>
-      <c r="AP13">
-        <v>0</v>
-      </c>
-      <c r="AQ13">
-        <v>0</v>
-      </c>
-      <c r="AR13">
-        <v>0</v>
-      </c>
-      <c r="AS13">
-        <v>0</v>
-      </c>
-      <c r="AT13">
-        <v>0</v>
-      </c>
-      <c r="AU13">
-        <v>0</v>
-      </c>
-      <c r="AV13">
-        <v>0</v>
-      </c>
-      <c r="AW13">
-        <v>0</v>
-      </c>
-      <c r="AX13">
-        <v>0</v>
-      </c>
-      <c r="AY13">
-        <v>0</v>
-      </c>
-      <c r="AZ13">
-        <v>0</v>
-      </c>
-      <c r="BA13">
-        <v>0</v>
-      </c>
-      <c r="BB13">
-        <v>1.62</v>
-      </c>
-      <c r="BC13">
-        <v>2.2</v>
-      </c>
-      <c r="BD13" s="3">
+        <v>111</v>
+      </c>
+      <c r="AL13" s="3">
         <v>45742.83333333334</v>
       </c>
     </row>
-    <row r="14" spans="1:56">
+    <row r="14" spans="1:38">
       <c r="A14" s="2">
         <v>45742</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="D14" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="F14" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -3015,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="L14">
         <v>1.89</v>
@@ -3090,87 +2334,33 @@
         <v>1.01</v>
       </c>
       <c r="AJ14" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK14" t="s">
-        <v>116</v>
-      </c>
-      <c r="AL14">
-        <v>1.17</v>
-      </c>
-      <c r="AM14">
-        <v>1.37</v>
-      </c>
-      <c r="AN14">
-        <v>1.85</v>
-      </c>
-      <c r="AO14">
-        <v>5</v>
-      </c>
-      <c r="AP14">
-        <v>1.72</v>
-      </c>
-      <c r="AQ14">
-        <v>2.17</v>
-      </c>
-      <c r="AR14">
-        <v>2.88</v>
-      </c>
-      <c r="AS14">
-        <v>3.9</v>
-      </c>
-      <c r="AT14">
-        <v>5.3</v>
-      </c>
-      <c r="AU14">
-        <v>1.98</v>
-      </c>
-      <c r="AV14">
-        <v>1.6</v>
-      </c>
-      <c r="AW14">
-        <v>1.35</v>
-      </c>
-      <c r="AX14">
-        <v>1.21</v>
-      </c>
-      <c r="AY14">
-        <v>1.11</v>
-      </c>
-      <c r="AZ14">
-        <v>0</v>
-      </c>
-      <c r="BA14">
-        <v>0</v>
-      </c>
-      <c r="BB14">
-        <v>1.62</v>
-      </c>
-      <c r="BC14">
-        <v>3.25</v>
-      </c>
-      <c r="BD14" s="3">
+        <v>98</v>
+      </c>
+      <c r="AL14" s="3">
         <v>45742.875</v>
       </c>
     </row>
-    <row r="15" spans="1:56">
+    <row r="15" spans="1:38">
       <c r="A15" s="2">
         <v>45742</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="E15" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="F15" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -3185,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="L15">
         <v>2.1</v>
@@ -3260,87 +2450,33 @@
         <v>1.28</v>
       </c>
       <c r="AJ15" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="AK15" t="s">
-        <v>116</v>
-      </c>
-      <c r="AL15">
-        <v>1.38</v>
-      </c>
-      <c r="AM15">
-        <v>1.25</v>
-      </c>
-      <c r="AN15">
-        <v>1.75</v>
-      </c>
-      <c r="AO15">
-        <v>14</v>
-      </c>
-      <c r="AP15">
-        <v>0</v>
-      </c>
-      <c r="AQ15">
-        <v>0</v>
-      </c>
-      <c r="AR15">
-        <v>2.1</v>
-      </c>
-      <c r="AS15">
-        <v>0</v>
-      </c>
-      <c r="AT15">
-        <v>0</v>
-      </c>
-      <c r="AU15">
-        <v>0</v>
-      </c>
-      <c r="AV15">
-        <v>0</v>
-      </c>
-      <c r="AW15">
-        <v>0</v>
-      </c>
-      <c r="AX15">
-        <v>0</v>
-      </c>
-      <c r="AY15">
-        <v>0</v>
-      </c>
-      <c r="AZ15">
-        <v>0</v>
-      </c>
-      <c r="BA15">
-        <v>0</v>
-      </c>
-      <c r="BB15">
-        <v>1.62</v>
-      </c>
-      <c r="BC15">
-        <v>2.2</v>
-      </c>
-      <c r="BD15" s="3">
+        <v>98</v>
+      </c>
+      <c r="AL15" s="3">
         <v>45742.95833333334</v>
       </c>
     </row>
-    <row r="16" spans="1:56">
+    <row r="16" spans="1:38">
       <c r="A16" s="2">
         <v>45742</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" t="s">
         <v>78</v>
       </c>
-      <c r="D16" t="s">
-        <v>81</v>
-      </c>
-      <c r="E16" t="s">
-        <v>96</v>
-      </c>
       <c r="F16" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -3355,7 +2491,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="L16">
         <v>2.88</v>
@@ -3430,66 +2566,12 @@
         <v>1.11</v>
       </c>
       <c r="AJ16" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="AK16" t="s">
-        <v>130</v>
-      </c>
-      <c r="AL16">
-        <v>1.58</v>
-      </c>
-      <c r="AM16">
-        <v>1.23</v>
-      </c>
-      <c r="AN16">
-        <v>1.3</v>
-      </c>
-      <c r="AO16">
-        <v>10</v>
-      </c>
-      <c r="AP16">
-        <v>0</v>
-      </c>
-      <c r="AQ16">
-        <v>0</v>
-      </c>
-      <c r="AR16">
-        <v>0</v>
-      </c>
-      <c r="AS16">
-        <v>0</v>
-      </c>
-      <c r="AT16">
-        <v>0</v>
-      </c>
-      <c r="AU16">
-        <v>0</v>
-      </c>
-      <c r="AV16">
-        <v>0</v>
-      </c>
-      <c r="AW16">
-        <v>0</v>
-      </c>
-      <c r="AX16">
-        <v>0</v>
-      </c>
-      <c r="AY16">
-        <v>0</v>
-      </c>
-      <c r="AZ16">
-        <v>0</v>
-      </c>
-      <c r="BA16">
-        <v>0</v>
-      </c>
-      <c r="BB16">
-        <v>2.25</v>
-      </c>
-      <c r="BC16">
-        <v>1.73</v>
-      </c>
-      <c r="BD16" s="3">
+        <v>112</v>
+      </c>
+      <c r="AL16" s="3">
         <v>45742.97916666666</v>
       </c>
     </row>
